--- a/mode_docx_gen/pmi_lodzt/lot_modes/ЛО Т_10.xlsx
+++ b/mode_docx_gen/pmi_lodzt/lot_modes/ЛО Т_10.xlsx
@@ -1113,8 +1113,8 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" s="2" t="n">
-        <v>1</v>
+      <c r="I2" t="n">
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -1550,9 +1550,9 @@
           <t>0</t>
         </is>
       </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
